--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\易碩\專案\newCoker\EtheriT.Coker.WebApplication\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FB4FD7-1174-473E-8DAF-747C499D58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E695C5-BAE6-4B82-8A2B-3269E5F835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="190">
   <si>
     <t>主料號</t>
   </si>
@@ -31,19 +31,10 @@
   </si>
   <si>
     <t>商品狀態</t>
-  </si>
-  <si>
-    <t>*產品簡介
-「圖片右邊
-標題下面」</t>
   </si>
   <si>
     <t>詳細說明
 「圖片右邊」</t>
-  </si>
-  <si>
-    <t>產品說明
-「下方區域」</t>
   </si>
   <si>
     <t>*媒體1
@@ -207,15 +198,18 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Visible</t>
+  </si>
+  <si>
+    <t>OnShelf</t>
+  </si>
+  <si>
     <t>Introduction</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Html</t>
-  </si>
-  <si>
     <t>Image1</t>
   </si>
   <si>
@@ -345,13 +339,16 @@
     <t>{{Products.Status}}</t>
   </si>
   <si>
+    <t>{{Products.Visible}}</t>
+  </si>
+  <si>
+    <t>{{Products.OnShelf}}</t>
+  </si>
+  <si>
     <t>{{Products.Introduction}}</t>
   </si>
   <si>
     <t>{{Products.Description}}</t>
-  </si>
-  <si>
-    <t>{{Products.Html}}</t>
   </si>
   <si>
     <t>{{Products.Image1}}</t>
@@ -587,34 +584,33 @@
     <t>{{TechCerts.Description}}</t>
   </si>
   <si>
-    <t>Visible</t>
-  </si>
-  <si>
-    <t>OnShelf</t>
-  </si>
-  <si>
-    <t>{{Products.Visible}}</t>
-  </si>
-  <si>
-    <t>{{Products.OnShelf}}</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">*商品名稱
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>不可空白</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <t>產品說明 HTML
+「下方區域」</t>
+  </si>
+  <si>
+    <t>產品說明 CSS
+「下方區域」</t>
+  </si>
+  <si>
+    <t>規格描述</t>
+  </si>
+  <si>
+    <t>SaveHtml</t>
+  </si>
+  <si>
+    <t>SaveCss</t>
+  </si>
+  <si>
+    <t>SpecDescription</t>
+  </si>
+  <si>
+    <t>{{Products.SaveHtml}}</t>
+  </si>
+  <si>
+    <t>{{Products.SaveCss}}</t>
+  </si>
+  <si>
+    <t>{{Products.SpecDescription}}</t>
   </si>
   <si>
     <r>
@@ -630,11 +626,11 @@
       </rPr>
       <t>ag6</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">上架
+      <t xml:space="preserve">價格
 </t>
     </r>
     <r>
@@ -646,16 +642,16 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>請輸入是或否</t>
+      <t>請輸入金額或「時價」</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="新細明體"/>
         <family val="1"/>
         <charset val="136"/>
@@ -665,7 +661,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="新細明體"/>
         <family val="1"/>
         <charset val="136"/>
@@ -684,7 +680,7 @@
       </rPr>
       <t>請輸入是或否</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -696,7 +692,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">價格
+      <t xml:space="preserve">上架
 </t>
     </r>
     <r>
@@ -708,9 +704,32 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>請輸入金額或「時價」</t>
+      <t>請輸入是或否</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*商品名稱
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>不可空白</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>*產品簡介
+「圖片右邊標題下面」</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -724,14 +743,6 @@
       <name val="新細明體"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -836,6 +847,13 @@
       <charset val="136"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -912,7 +930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -952,58 +970,55 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1012,25 +1027,31 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1266,536 +1287,556 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW200"/>
+  <dimension ref="A1:AY200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="34.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="40" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="22" customWidth="1"/>
-    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="52.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="78.125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="90.125" style="24" customWidth="1"/>
-    <col min="10" max="10" width="27.125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="24.5" style="5" customWidth="1"/>
-    <col min="12" max="15" width="22.25" style="5" customWidth="1"/>
-    <col min="16" max="16" width="26.75" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15" style="1" customWidth="1"/>
-    <col min="18" max="18" width="24" style="4" customWidth="1"/>
-    <col min="19" max="19" width="15.25" style="1" customWidth="1"/>
-    <col min="20" max="20" width="26.75" style="4" customWidth="1"/>
-    <col min="21" max="21" width="18.875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="27.625" style="5" customWidth="1"/>
-    <col min="23" max="23" width="26.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="31.875" style="5" customWidth="1"/>
-    <col min="25" max="25" width="26.75" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.25" style="5" customWidth="1"/>
-    <col min="27" max="27" width="26.75" style="1" customWidth="1"/>
-    <col min="28" max="30" width="22.25" style="5" customWidth="1"/>
-    <col min="31" max="31" width="22.5" style="6" customWidth="1"/>
-    <col min="32" max="32" width="21.75" style="6" customWidth="1"/>
-    <col min="33" max="33" width="20.125" style="7" customWidth="1"/>
-    <col min="34" max="34" width="38.125" style="7" customWidth="1"/>
-    <col min="35" max="35" width="13.75" style="7" customWidth="1"/>
-    <col min="36" max="36" width="8.875" style="7" customWidth="1"/>
-    <col min="37" max="37" width="6.5" style="7" customWidth="1"/>
-    <col min="38" max="39" width="9" style="5"/>
-    <col min="40" max="40" width="14" style="5" customWidth="1"/>
-    <col min="41" max="41" width="16" style="5" customWidth="1"/>
+    <col min="9" max="9" width="90.125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="27.125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="24.5" style="5" customWidth="1"/>
+    <col min="13" max="16" width="22.25" style="5" customWidth="1"/>
+    <col min="17" max="17" width="26.75" style="5" customWidth="1"/>
+    <col min="18" max="18" width="15" style="1" customWidth="1"/>
+    <col min="19" max="19" width="24" style="4" customWidth="1"/>
+    <col min="20" max="20" width="15.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="26.75" style="4" customWidth="1"/>
+    <col min="22" max="22" width="18.875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="27.625" style="5" customWidth="1"/>
+    <col min="24" max="24" width="26.75" style="1" customWidth="1"/>
+    <col min="25" max="25" width="31.875" style="5" customWidth="1"/>
+    <col min="26" max="26" width="26.75" style="1" customWidth="1"/>
+    <col min="27" max="27" width="22.25" style="5" customWidth="1"/>
+    <col min="28" max="28" width="26.75" style="1" customWidth="1"/>
+    <col min="29" max="31" width="22.25" style="5" customWidth="1"/>
+    <col min="32" max="32" width="22.5" style="6" customWidth="1"/>
+    <col min="33" max="33" width="21.75" style="6" customWidth="1"/>
+    <col min="34" max="34" width="20.125" style="7" customWidth="1"/>
+    <col min="35" max="35" width="38.125" style="7" customWidth="1"/>
+    <col min="36" max="36" width="13.75" style="7" customWidth="1"/>
+    <col min="37" max="37" width="8.875" style="7" customWidth="1"/>
+    <col min="38" max="38" width="20" customWidth="1"/>
+    <col min="39" max="39" width="6.5" style="7" customWidth="1"/>
+    <col min="40" max="41" width="9" style="5"/>
     <col min="42" max="42" width="14" style="5" customWidth="1"/>
-    <col min="43" max="43" width="12" customWidth="1"/>
-    <col min="44" max="47" width="15.25" style="4" customWidth="1"/>
-    <col min="48" max="48" width="10.375" style="4" customWidth="1"/>
-    <col min="49" max="49" width="15.25" style="4" customWidth="1"/>
-    <col min="50" max="16384" width="9" style="5"/>
+    <col min="43" max="43" width="16" style="5" customWidth="1"/>
+    <col min="44" max="44" width="14" style="5" customWidth="1"/>
+    <col min="45" max="45" width="12" customWidth="1"/>
+    <col min="46" max="49" width="15.25" style="4" customWidth="1"/>
+    <col min="50" max="50" width="10.375" style="4" customWidth="1"/>
+    <col min="51" max="51" width="15.25" style="4" customWidth="1"/>
+    <col min="52" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:51" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="38" t="s">
+      <c r="C1" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G1" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="M1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="P1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="Q1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="S1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="U1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="W1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="X1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="Y1" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="Z1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="AA1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="AB1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="27" t="s">
+      <c r="AC1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AD1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AE1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AF1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AG1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AH1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AI1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" s="25" t="s">
+      <c r="AJ1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" s="12" t="s">
+      <c r="AK1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="25" t="s">
+      <c r="AL1" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AN1" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" s="10" t="s">
+      <c r="AO1" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="27" t="s">
+      <c r="AP1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="27" t="s">
+      <c r="AQ1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" s="27" t="s">
+      <c r="AR1" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AS1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" s="27" t="s">
+      <c r="AT1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AP1" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="AQ1" s="27" t="s">
+      <c r="AU1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AV1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AW1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="11" t="s">
+      <c r="AX1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AY1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="8" t="s">
+      <c r="B2" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="D2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="E2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="J2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K2" t="s">
         <v>51</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>53</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>54</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>55</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>56</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>57</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="S2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="T2" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="U2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="V2" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="W2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="X2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="Y2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Z2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="AA2" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AB2" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AC2" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AD2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AE2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AF2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="AE2" s="18" t="s">
+      <c r="AG2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="AF2" s="18" t="s">
+      <c r="AH2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AG2" s="18" t="s">
+      <c r="AI2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AH2" s="18" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AK2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AL2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AM2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="AK2" s="18" t="s">
+      <c r="AN2" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="AL2" s="28" t="s">
+      <c r="AO2" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="28" t="s">
+      <c r="AP2" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="32" t="s">
+      <c r="AQ2" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="31" t="s">
+      <c r="AR2" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="32" t="s">
+      <c r="AS2" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="AQ2" s="32" t="s">
+      <c r="AT2" t="s">
         <v>85</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>86</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>87</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>88</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>89</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" s="28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
-      <c r="AW2" s="29" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>91</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" t="s">
         <v>94</v>
       </c>
-      <c r="E3" t="s">
-        <v>177</v>
-      </c>
       <c r="F3" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>101</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>102</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>103</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>105</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>106</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>107</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>108</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>109</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>110</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>111</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>112</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>114</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>115</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>116</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>117</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>121</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>122</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>123</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>124</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AL3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM3" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="AL3" s="28" t="s">
+      <c r="AN3" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="AM3" s="28" t="s">
+      <c r="AO3" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="AN3" s="32" t="s">
+      <c r="AP3" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="AO3" s="31" t="s">
+      <c r="AQ3" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="AP3" s="34" t="s">
+      <c r="AR3" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="AQ3" s="32" t="s">
+      <c r="AS3" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="AR3" s="4" t="s">
+      <c r="AT3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AU3" t="s">
         <v>133</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AV3" t="s">
         <v>134</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AW3" t="s">
         <v>135</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AX3" t="s">
         <v>136</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AY3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F4"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F6"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="F16"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
@@ -2351,7 +2392,7 @@
       <c r="F200"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2372,46 +2413,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2435,32 +2476,32 @@
         <v>154</v>
       </c>
       <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
         <v>86</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>87</v>
       </c>
-      <c r="I3" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>158</v>
       </c>
       <c r="E4" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>160</v>
       </c>
       <c r="G4" t="s">
@@ -2474,121 +2515,121 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2606,16 +2647,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>165</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>167</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -2624,18 +2665,18 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2657,7 +2698,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\易碩\專案\newCoker\EtheriT.Coker.WebApplication\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E695C5-BAE6-4B82-8A2B-3269E5F835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A463F33-1410-4A8D-AB93-8B980417102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="191">
   <si>
     <t>主料號</t>
   </si>
@@ -204,9 +204,6 @@
     <t>OnShelf</t>
   </si>
   <si>
-    <t>Introduction</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -593,9 +590,6 @@
   </si>
   <si>
     <t>規格描述</t>
-  </si>
-  <si>
-    <t>SaveHtml</t>
   </si>
   <si>
     <t>SaveCss</t>
@@ -729,6 +723,18 @@
   <si>
     <t>*產品簡介
 「圖片右邊標題下面」</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Introduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SaveHtml</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -930,7 +936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -997,9 +1003,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1039,20 +1042,20 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1298,7 +1301,7 @@
     <col min="6" max="6" width="19.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="52.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="78.125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="90.125" style="23" customWidth="1"/>
+    <col min="9" max="9" width="90.125" style="22" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="27.125" style="5" customWidth="1"/>
     <col min="12" max="12" width="24.5" style="5" customWidth="1"/>
@@ -1342,29 +1345,29 @@
       <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F1" s="34" t="s">
+      <c r="E1" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" s="37" t="s">
         <v>187</v>
-      </c>
-      <c r="G1" s="40" t="s">
-        <v>189</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>176</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>4</v>
@@ -1396,37 +1399,37 @@
       <c r="T1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="25" t="s">
         <v>14</v>
       </c>
       <c r="V1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="W1" s="25" t="s">
         <v>16</v>
       </c>
       <c r="X1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Y1" s="25" t="s">
         <v>18</v>
       </c>
       <c r="Z1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="26" t="s">
+      <c r="AA1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="26" t="s">
+      <c r="AB1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="26" t="s">
+      <c r="AC1" s="25" t="s">
         <v>22</v>
       </c>
       <c r="AD1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AE1" s="26" t="s">
+      <c r="AE1" s="25" t="s">
         <v>24</v>
       </c>
       <c r="AF1" s="10" t="s">
@@ -1435,40 +1438,40 @@
       <c r="AG1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AH1" s="24" t="s">
+      <c r="AH1" s="23" t="s">
         <v>27</v>
       </c>
       <c r="AI1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AJ1" s="24" t="s">
+      <c r="AJ1" s="23" t="s">
         <v>29</v>
       </c>
       <c r="AK1" s="12" t="s">
         <v>30</v>
       </c>
       <c r="AL1" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" s="26" t="s">
+      <c r="AN1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="26" t="s">
+      <c r="AO1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="26" t="s">
+      <c r="AP1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="26" t="s">
+      <c r="AQ1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="AS1" s="26" t="s">
+      <c r="AR1" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="AS1" s="25" t="s">
         <v>36</v>
       </c>
       <c r="AT1" s="11" t="s">
@@ -1509,295 +1512,295 @@
       <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="J2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="W2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="X2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI2" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL2" t="s">
         <v>178</v>
       </c>
-      <c r="J2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>57</v>
-      </c>
-      <c r="R2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="V2" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="W2" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="X2" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y2" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z2" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA2" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB2" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE2" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF2" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH2" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI2" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ2" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AM2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="AL2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AM2" s="17" t="s">
+      <c r="AN2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="27" t="s">
+      <c r="AO2" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="27" t="s">
+      <c r="AP2" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="31" t="s">
+      <c r="AQ2" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AQ2" s="30" t="s">
+      <c r="AR2" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="AR2" s="31" t="s">
+      <c r="AS2" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="AS2" s="31" t="s">
+      <c r="AT2" t="s">
         <v>84</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>85</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>86</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>87</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>88</v>
       </c>
-      <c r="AX2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY2" s="28" t="s">
-        <v>184</v>
+      <c r="AY2" s="27" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" t="s">
         <v>93</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>94</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" t="s">
         <v>96</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T3" t="s">
+        <v>106</v>
+      </c>
+      <c r="U3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V3" t="s">
+        <v>108</v>
+      </c>
+      <c r="W3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG3" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL3" t="s">
         <v>181</v>
       </c>
-      <c r="J3" t="s">
-        <v>182</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="N3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>104</v>
-      </c>
-      <c r="R3" t="s">
-        <v>105</v>
-      </c>
-      <c r="S3" t="s">
-        <v>106</v>
-      </c>
-      <c r="T3" t="s">
-        <v>107</v>
-      </c>
-      <c r="U3" t="s">
-        <v>108</v>
-      </c>
-      <c r="V3" t="s">
-        <v>109</v>
-      </c>
-      <c r="W3" t="s">
-        <v>110</v>
-      </c>
-      <c r="X3" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK3" t="s">
+      <c r="AM3" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AL3" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AN3" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AN3" s="27" t="s">
+      <c r="AO3" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AP3" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="AP3" s="31" t="s">
+      <c r="AQ3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AQ3" s="30" t="s">
+      <c r="AR3" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="AR3" s="33" t="s">
+      <c r="AS3" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="AS3" s="31" t="s">
+      <c r="AT3" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AU3" t="s">
         <v>132</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AV3" t="s">
         <v>133</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AW3" t="s">
         <v>134</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>135</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>136</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
@@ -2413,105 +2416,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="B2" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="D2" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="I2" s="31" t="s">
         <v>147</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
         <v>149</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>150</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>151</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>152</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>153</v>
       </c>
-      <c r="F3" t="s">
-        <v>154</v>
-      </c>
       <c r="G3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s">
         <v>85</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>86</v>
-      </c>
-      <c r="I3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" t="s">
         <v>158</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" t="s">
         <v>160</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>161</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>162</v>
-      </c>
-      <c r="I4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2593,36 +2596,36 @@
       <c r="D17" s="13"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2648,19 +2651,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="E1" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2671,30 +2674,30 @@
         <v>45</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
         <v>170</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>171</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>172</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>173</v>
-      </c>
-      <c r="E3" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>主料號</t>
   </si>
@@ -736,6 +736,15 @@
   <si>
     <t>SaveHtml</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品 ID</t>
+  </si>
+  <si>
+    <t>ProductId</t>
+  </si>
+  <si>
+    <t>{{Products.ProductId}}</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY200"/>
+  <dimension ref="A1:AZ200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -1338,7 +1347,7 @@
     <col min="52" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1492,8 +1501,11 @@
       <c r="AY1" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ1" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1647,8 +1659,11 @@
       <c r="AY2" s="27" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ2" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1801,6 +1816,9 @@
       </c>
       <c r="AY3" t="s">
         <v>136</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">

--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\易碩\專案\newCoker\EtheriT.Coker.WebApplication\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A463F33-1410-4A8D-AB93-8B980417102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F37658-75E2-40ED-AD2A-510C2F07858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="197">
   <si>
     <t>主料號</t>
   </si>
@@ -285,9 +285,6 @@
     <t>Spec2Name</t>
   </si>
   <si>
-    <t>Spec2</t>
-  </si>
-  <si>
     <t>Stock</t>
   </si>
   <si>
@@ -427,12 +424,6 @@
   </si>
   <si>
     <t>{{Products.Spec2}}</t>
-  </si>
-  <si>
-    <t>{{Products.Stock}}</t>
-  </si>
-  <si>
-    <t>{{Products.Min_Qty}}</t>
   </si>
   <si>
     <t>{{Products.Alert_Qty}}</t>
@@ -595,16 +586,10 @@
     <t>SaveCss</t>
   </si>
   <si>
-    <t>SpecDescription</t>
-  </si>
-  <si>
     <t>{{Products.SaveHtml}}</t>
   </si>
   <si>
     <t>{{Products.SaveCss}}</t>
-  </si>
-  <si>
-    <t>{{Products.SpecDescription}}</t>
   </si>
   <si>
     <r>
@@ -745,6 +730,40 @@
   </si>
   <si>
     <t>{{Products.ProductId}}</t>
+  </si>
+  <si>
+    <t>SpecDescription</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>規格圖
+請輸入檔案相對位置
+如：../upload/img1.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spec2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecImage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{Products.SpecDescription}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{Products.Stock}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{Products.Min_Qty}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{Products.SpecImage}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -945,7 +964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1065,6 +1084,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1299,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ200"/>
+  <dimension ref="A1:BA200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -1334,7 +1356,7 @@
     <col min="35" max="35" width="38.125" style="7" customWidth="1"/>
     <col min="36" max="36" width="13.75" style="7" customWidth="1"/>
     <col min="37" max="37" width="8.875" style="7" customWidth="1"/>
-    <col min="38" max="38" width="20" customWidth="1"/>
+    <col min="38" max="38" width="25.125" customWidth="1"/>
     <col min="39" max="39" width="6.5" style="7" customWidth="1"/>
     <col min="40" max="41" width="9" style="5"/>
     <col min="42" max="42" width="14" style="5" customWidth="1"/>
@@ -1347,7 +1369,7 @@
     <col min="52" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1355,28 +1377,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>4</v>
@@ -1459,53 +1481,56 @@
       <c r="AK1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="AM1" s="10" t="s">
+      <c r="AL1" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM1" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" s="25" t="s">
+      <c r="AO1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="25" t="s">
+      <c r="AP1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="25" t="s">
+      <c r="AQ1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="25" t="s">
+      <c r="AR1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="AS1" s="25" t="s">
+      <c r="AS1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AT1" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="11" t="s">
+      <c r="AU1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AV1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AW1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AX1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" s="8" t="s">
+      <c r="AY1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="8" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA1" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1525,16 +1550,16 @@
         <v>48</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K2" t="s">
         <v>50</v>
@@ -1614,250 +1639,256 @@
       <c r="AJ2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AK2" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AN2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AL2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AM2" s="17" t="s">
+      <c r="AO2" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="AN2" s="26" t="s">
+      <c r="AP2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AQ2" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="AP2" s="30" t="s">
+      <c r="AR2" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AQ2" s="29" t="s">
+      <c r="AS2" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="AR2" s="30" t="s">
+      <c r="AT2" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="AS2" s="30" t="s">
+      <c r="AU2" t="s">
         <v>83</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>84</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>85</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>86</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>87</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA2" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>88</v>
       </c>
-      <c r="AY2" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="AZ2" s="27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" t="s">
         <v>92</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>93</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" t="s">
         <v>95</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" t="s">
         <v>99</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>100</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>101</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>102</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>103</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>104</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>105</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>106</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>107</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>108</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>109</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>110</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>111</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>112</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>113</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>114</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>115</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>116</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AH3" t="s">
         <v>119</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>120</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>121</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>122</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM3" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="AO3" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="AP3" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AL3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AQ3" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="AN3" s="26" t="s">
+      <c r="AR3" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AO3" s="26" t="s">
+      <c r="AS3" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="AP3" s="30" t="s">
+      <c r="AT3" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="AQ3" s="29" t="s">
+      <c r="AU3" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AR3" s="32" t="s">
+      <c r="AV3" t="s">
         <v>129</v>
       </c>
-      <c r="AS3" s="30" t="s">
+      <c r="AW3" t="s">
         <v>130</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AX3" t="s">
         <v>131</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AY3" t="s">
         <v>132</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AZ3" t="s">
         <v>133</v>
       </c>
-      <c r="AW3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="BA3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F4"/>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F5"/>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F6"/>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="F16"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
@@ -2435,7 +2466,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -2443,96 +2474,96 @@
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
       <c r="G1" s="39" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H1" s="39"/>
       <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="H2" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>144</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" t="s">
         <v>148</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>149</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>150</v>
       </c>
-      <c r="D3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" t="s">
-        <v>153</v>
-      </c>
       <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
         <v>84</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>85</v>
-      </c>
-      <c r="I3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="E4" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="G4" t="s">
         <v>157</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="I4" t="s">
         <v>159</v>
-      </c>
-      <c r="G4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2669,19 +2700,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="E1" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,7 +2723,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>50</v>
@@ -2703,19 +2734,19 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" t="s">
         <v>169</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>170</v>
-      </c>
-      <c r="C3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\易碩\專案\newCoker\EtheriT.Coker.WebApplication\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Cocker\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F37658-75E2-40ED-AD2A-510C2F07858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F6FE0B-2FA9-4825-B346-AF2AA0E2AA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="商品" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="200">
   <si>
     <t>主料號</t>
   </si>
@@ -763,6 +763,19 @@
   </si>
   <si>
     <t>{{Products.SpecImage}}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>規格是否顯示
+請輸入是或否</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecVisible</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{Products.SpecVisible}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1079,14 +1092,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1321,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA200"/>
+  <dimension ref="A1:BB200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -1356,20 +1369,20 @@
     <col min="35" max="35" width="38.125" style="7" customWidth="1"/>
     <col min="36" max="36" width="13.75" style="7" customWidth="1"/>
     <col min="37" max="37" width="8.875" style="7" customWidth="1"/>
-    <col min="38" max="38" width="25.125" customWidth="1"/>
-    <col min="39" max="39" width="6.5" style="7" customWidth="1"/>
-    <col min="40" max="41" width="9" style="5"/>
-    <col min="42" max="42" width="14" style="5" customWidth="1"/>
-    <col min="43" max="43" width="16" style="5" customWidth="1"/>
-    <col min="44" max="44" width="14" style="5" customWidth="1"/>
-    <col min="45" max="45" width="12" customWidth="1"/>
-    <col min="46" max="49" width="15.25" style="4" customWidth="1"/>
-    <col min="50" max="50" width="10.375" style="4" customWidth="1"/>
-    <col min="51" max="51" width="15.25" style="4" customWidth="1"/>
-    <col min="52" max="16384" width="9" style="5"/>
+    <col min="38" max="39" width="25.125" customWidth="1"/>
+    <col min="40" max="40" width="6.5" style="7" customWidth="1"/>
+    <col min="41" max="42" width="9" style="5"/>
+    <col min="43" max="43" width="14" style="5" customWidth="1"/>
+    <col min="44" max="44" width="16" style="5" customWidth="1"/>
+    <col min="45" max="45" width="14" style="5" customWidth="1"/>
+    <col min="46" max="46" width="12" customWidth="1"/>
+    <col min="47" max="50" width="15.25" style="4" customWidth="1"/>
+    <col min="51" max="51" width="10.375" style="4" customWidth="1"/>
+    <col min="52" max="52" width="15.25" style="4" customWidth="1"/>
+    <col min="53" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" s="11" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1470,67 +1483,70 @@
         <v>26</v>
       </c>
       <c r="AH1" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI1" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="AI1" s="12" t="s">
+      <c r="AJ1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AJ1" s="23" t="s">
+      <c r="AK1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="AK1" s="12" t="s">
+      <c r="AL1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" s="25" t="s">
+      <c r="AM1" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="AM1" s="12" t="s">
+      <c r="AN1" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AN1" s="10" t="s">
+      <c r="AO1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="25" t="s">
+      <c r="AP1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="25" t="s">
+      <c r="AQ1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="25" t="s">
+      <c r="AR1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" s="25" t="s">
+      <c r="AS1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="35" t="s">
+      <c r="AT1" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="AT1" s="25" t="s">
+      <c r="AU1" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AV1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AW1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AX1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="11" t="s">
+      <c r="AY1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="8" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="BA1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BB1" s="8" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1630,68 +1646,71 @@
       <c r="AG2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AH2" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AI2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="AI2" s="17" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AJ2" s="17" t="s">
+      <c r="AK2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AK2" s="6" t="s">
+      <c r="AL2" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="AM2" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="AM2" s="5" t="s">
+      <c r="AN2" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="AN2" s="17" t="s">
+      <c r="AO2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AP2" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="AP2" s="26" t="s">
+      <c r="AQ2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="AQ2" s="30" t="s">
+      <c r="AR2" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="AR2" s="29" t="s">
+      <c r="AS2" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AS2" s="30" t="s">
+      <c r="AT2" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="AT2" s="30" t="s">
+      <c r="AU2" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>83</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>84</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>85</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>86</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>87</v>
       </c>
-      <c r="AZ2" s="27" t="s">
+      <c r="BA2" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="BA2" s="27" t="s">
+      <c r="BB2" s="27" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -1791,104 +1810,107 @@
       <c r="AG3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AH3" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI3" t="s">
         <v>119</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>120</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>121</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>122</v>
       </c>
-      <c r="AL3" s="5" t="s">
+      <c r="AM3" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="AM3" s="5" t="s">
+      <c r="AN3" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AO3" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="AO3" s="40" t="s">
+      <c r="AP3" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="AP3" s="26" t="s">
+      <c r="AQ3" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AQ3" s="30" t="s">
+      <c r="AR3" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="AR3" s="29" t="s">
+      <c r="AS3" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="32" t="s">
+      <c r="AT3" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="AT3" s="30" t="s">
+      <c r="AU3" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="AU3" s="4" t="s">
+      <c r="AV3" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AW3" t="s">
         <v>129</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>130</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>131</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AZ3" t="s">
         <v>132</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BA3" t="s">
         <v>133</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BB3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F4"/>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F5"/>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F6"/>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="F16"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
@@ -2465,19 +2487,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
